--- a/app/templates/warehouse_bulk_upload.xlsx
+++ b/app/templates/warehouse_bulk_upload.xlsx
@@ -428,6 +428,13 @@
   </sheetPr>
   <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="31" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -530,6 +537,10 @@
   </sheetPr>
   <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="41" customWidth="1" min="2" max="2"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
